--- a/METAS 2026.xlsx
+++ b/METAS 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoequatorialenergia-my.sharepoint.com/personal/suene_silva_equatorialenergia_com_br/Documents/SUENE MARQUES/SITE PRODUÇÃO 2.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{11417170-F61A-4D10-A07B-3C3DC6DE4552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C5923A3-44CA-4CFD-8A8F-CC35446773F3}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{11417170-F61A-4D10-A07B-3C3DC6DE4552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F109BFE8-A22A-46B6-8216-7B086EE00BD9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{782DD64E-CD9D-4905-9FBE-C3B5A61A20CB}"/>
+    <workbookView xWindow="11268" yWindow="936" windowWidth="11268" windowHeight="11292" xr2:uid="{782DD64E-CD9D-4905-9FBE-C3B5A61A20CB}"/>
   </bookViews>
   <sheets>
     <sheet name="METAS 2026" sheetId="1" r:id="rId1"/>
@@ -2251,13 +2251,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>0</v>
+        <v>121325.46699797094</v>
       </c>
       <c r="B98" t="s">
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D98" t="s">
         <v>16</v>
@@ -2268,44 +2268,44 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>40400.432383580723</v>
+        <v>83051.513151445775</v>
       </c>
       <c r="B99" t="s">
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E99" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>78277.525466597726</v>
+        <v>27683.837717148592</v>
       </c>
       <c r="B100" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C100" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D100" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E100" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>121325.46699797094</v>
+        <v>119059.91107745597</v>
       </c>
       <c r="B101" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C101" t="s">
         <v>7</v>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>161737.67421044351</v>
+        <v>297217.6683430897</v>
       </c>
       <c r="B102" t="s">
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D102" t="s">
         <v>16</v>
@@ -2336,44 +2336,44 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>204863.2298231702</v>
+        <v>221470.70173718871</v>
       </c>
       <c r="B103" t="s">
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E103" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>250849.30979147152</v>
+        <v>64595.621340013371</v>
       </c>
       <c r="B104" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E104" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>297217.6683430897</v>
+        <v>294350.69908188772</v>
       </c>
       <c r="B105" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
         <v>11</v>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>339544.68399856583</v>
+        <v>40400.432383580723</v>
       </c>
       <c r="B106" t="s">
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D106" t="s">
         <v>16</v>
@@ -2455,13 +2455,13 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>0</v>
+        <v>27683.837717148592</v>
       </c>
       <c r="B110" t="s">
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D110" t="s">
         <v>22</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>27683.837717148592</v>
+        <v>9227.9459057162003</v>
       </c>
       <c r="B111" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C111" t="s">
         <v>5</v>
@@ -2489,47 +2489,47 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>55367.675434297184</v>
+        <v>35694.402736386401</v>
       </c>
       <c r="B112" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C112" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D112" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E112" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <v>83051.513151445775</v>
+        <v>0</v>
       </c>
       <c r="B113" t="s">
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D113" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E113" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>110735.35086859437</v>
+        <v>0</v>
       </c>
       <c r="B114" t="s">
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D114" t="s">
         <v>22</v>
@@ -2540,13 +2540,13 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
-        <v>147647.13449145915</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C115" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D115" t="s">
         <v>22</v>
@@ -2557,47 +2557,47 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>184558.91811432393</v>
+        <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C116" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D116" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E116" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>221470.70173718871</v>
+        <v>250849.30979147152</v>
       </c>
       <c r="B117" t="s">
         <v>3</v>
       </c>
       <c r="C117" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D117" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E117" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>258382.48536005348</v>
+        <v>184558.91811432393</v>
       </c>
       <c r="B118" t="s">
         <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D118" t="s">
         <v>22</v>
@@ -2665,7 +2665,7 @@
         <v>3</v>
       </c>
       <c r="C122" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D122" t="s">
         <v>22</v>
@@ -2676,30 +2676,30 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>127956.7289673512</v>
+        <v>85493.396144889877</v>
       </c>
       <c r="B123" t="s">
         <v>3</v>
       </c>
       <c r="C123" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D123" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E123" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>127956.7289673512</v>
+        <v>63978.364483675607</v>
       </c>
       <c r="B124" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C124" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D124" t="s">
         <v>22</v>
@@ -2710,19 +2710,19 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>127956.7289673512</v>
+        <v>113994.59602698994</v>
       </c>
       <c r="B125" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C125" t="s">
         <v>7</v>
       </c>
       <c r="D125" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E125" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -2733,7 +2733,7 @@
         <v>3</v>
       </c>
       <c r="C126" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D126" t="s">
         <v>22</v>
@@ -2744,30 +2744,30 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>191935.0934510268</v>
+        <v>102256.80715369183</v>
       </c>
       <c r="B127" t="s">
         <v>3</v>
       </c>
       <c r="C127" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D127" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E127" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>191935.0934510268</v>
+        <v>63978.364483675607</v>
       </c>
       <c r="B128" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C128" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D128" t="s">
         <v>22</v>
@@ -2778,30 +2778,30 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>191935.0934510268</v>
+        <v>122285.1121016801</v>
       </c>
       <c r="B129" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C129" t="s">
         <v>11</v>
       </c>
       <c r="D129" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E129" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>191935.0934510268</v>
+        <v>127956.7289673512</v>
       </c>
       <c r="B130" t="s">
         <v>3</v>
       </c>
       <c r="C130" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D130" t="s">
         <v>22</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>87169.737245770084</v>
+        <v>80464.3728422493</v>
       </c>
       <c r="B134" t="s">
         <v>3</v>
       </c>
       <c r="C134" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D134" t="s">
         <v>16</v>
@@ -2880,30 +2880,30 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
-        <v>80464.3728422493</v>
+        <v>63978.364483675607</v>
       </c>
       <c r="B135" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C135" t="s">
         <v>5</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E135" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>93875.101649290853</v>
+        <v>109849.33798964485</v>
       </c>
       <c r="B136" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C136" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D136" t="s">
         <v>16</v>
@@ -2914,30 +2914,30 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
-        <v>85493.396144889877</v>
+        <v>127956.7289673512</v>
       </c>
       <c r="B137" t="s">
         <v>3</v>
       </c>
       <c r="C137" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D137" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E137" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>102256.80715369183</v>
+        <v>87169.737245770084</v>
       </c>
       <c r="B138" t="s">
         <v>3</v>
       </c>
       <c r="C138" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D138" t="s">
         <v>16</v>
@@ -2948,30 +2948,30 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>110638.51265809278</v>
+        <v>63978.364483675607</v>
       </c>
       <c r="B139" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C139" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E139" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
-        <v>110638.5126580928</v>
+        <v>105704.07995229975</v>
       </c>
       <c r="B140" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C140" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D140" t="s">
         <v>16</v>
@@ -2982,30 +2982,30 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>102256.80715369183</v>
+        <v>191935.0934510268</v>
       </c>
       <c r="B141" t="s">
         <v>3</v>
       </c>
       <c r="C141" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D141" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
-        <v>98904.124951931444</v>
+        <v>110638.5126580928</v>
       </c>
       <c r="B142" t="s">
         <v>3</v>
       </c>
       <c r="C142" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D142" t="s">
         <v>16</v>
@@ -4291,13 +4291,13 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
-        <v>0</v>
+        <v>55367.675434297176</v>
       </c>
       <c r="B218" t="s">
         <v>32</v>
       </c>
       <c r="C218" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D218" t="s">
         <v>22</v>
@@ -4308,47 +4308,47 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
-        <v>9227.9459057162003</v>
+        <v>247829.35310129516</v>
       </c>
       <c r="B219" t="s">
         <v>32</v>
       </c>
       <c r="C219" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D219" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E219" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
-        <v>18455.891811432397</v>
+        <v>204863.2298231702</v>
       </c>
       <c r="B220" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C220" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D220" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E220" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
-        <v>27683.837717148592</v>
+        <v>147647.13449145915</v>
       </c>
       <c r="B221" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C221" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D221" t="s">
         <v>22</v>
@@ -4359,13 +4359,13 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
-        <v>36911.783622864787</v>
+        <v>46139.729528580981</v>
       </c>
       <c r="B222" t="s">
         <v>32</v>
       </c>
       <c r="C222" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D222" t="s">
         <v>22</v>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
-        <v>46139.729528580981</v>
+        <v>203005.1727457745</v>
       </c>
       <c r="B223" t="s">
         <v>32</v>
@@ -4385,38 +4385,38 @@
         <v>9</v>
       </c>
       <c r="D223" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E223" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
-        <v>55367.675434297176</v>
+        <v>161737.67421044351</v>
       </c>
       <c r="B224" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C224" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D224" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E224" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
-        <v>64595.621340013371</v>
+        <v>110735.35086859437</v>
       </c>
       <c r="B225" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C225" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D225" t="s">
         <v>22</v>
@@ -4427,13 +4427,13 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
-        <v>73823.567245729573</v>
+        <v>36911.783622864787</v>
       </c>
       <c r="B226" t="s">
         <v>32</v>
       </c>
       <c r="C226" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D226" t="s">
         <v>22</v>
@@ -4495,13 +4495,13 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
-        <v>0</v>
+        <v>160483.5764073852</v>
       </c>
       <c r="B230" t="s">
         <v>32</v>
       </c>
       <c r="C230" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D230" t="s">
         <v>16</v>
@@ -4512,13 +4512,13 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
-        <v>35694.402736386401</v>
+        <v>78277.525466597726</v>
       </c>
       <c r="B231" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C231" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D231" t="s">
         <v>16</v>
@@ -4529,47 +4529,47 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
-        <v>74235.730721935324</v>
+        <v>55367.675434297184</v>
       </c>
       <c r="B232" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C232" t="s">
         <v>6</v>
       </c>
       <c r="D232" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E232" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
-        <v>119059.91107745597</v>
+        <v>18455.891811432397</v>
       </c>
       <c r="B233" t="s">
         <v>32</v>
       </c>
       <c r="C233" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D233" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E233" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
-        <v>160483.5764073852</v>
+        <v>74235.730721935324</v>
       </c>
       <c r="B234" t="s">
         <v>32</v>
       </c>
       <c r="C234" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D234" t="s">
         <v>16</v>
@@ -4580,13 +4580,13 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
-        <v>203005.1727457745</v>
+        <v>339544.68399856583</v>
       </c>
       <c r="B235" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C235" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D235" t="s">
         <v>16</v>
@@ -4597,36 +4597,36 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
-        <v>247829.35310129516</v>
+        <v>258382.48536005348</v>
       </c>
       <c r="B236" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C236" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D236" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E236" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
-        <v>294350.69908188772</v>
+        <v>73823.567245729573</v>
       </c>
       <c r="B237" t="s">
         <v>32</v>
       </c>
       <c r="C237" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E237" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -4909,7 +4909,7 @@
         <v>32</v>
       </c>
       <c r="C254" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D254" t="s">
         <v>22</v>
@@ -4920,30 +4920,30 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
-        <v>63978.364483675607</v>
+        <v>130575.62817637029</v>
       </c>
       <c r="B255" t="s">
         <v>32</v>
       </c>
       <c r="C255" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D255" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E255" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
-        <v>63978.364483675607</v>
+        <v>191935.0934510268</v>
       </c>
       <c r="B256" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C256" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D256" t="s">
         <v>22</v>
@@ -4954,19 +4954,19 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
-        <v>63978.364483675607</v>
+        <v>110638.51265809278</v>
       </c>
       <c r="B257" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C257" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D257" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E257" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
@@ -4977,7 +4977,7 @@
         <v>32</v>
       </c>
       <c r="C258" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D258" t="s">
         <v>22</v>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
-        <v>63978.364483675607</v>
+        <v>124357.74112035264</v>
       </c>
       <c r="B259" t="s">
         <v>32</v>
@@ -4997,21 +4997,21 @@
         <v>9</v>
       </c>
       <c r="D259" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E259" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
-        <v>63978.364483675607</v>
+        <v>191935.0934510268</v>
       </c>
       <c r="B260" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C260" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D260" t="s">
         <v>22</v>
@@ -5022,19 +5022,19 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
-        <v>63978.364483675607</v>
+        <v>102256.80715369183</v>
       </c>
       <c r="B261" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C261" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D261" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E261" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
@@ -5045,7 +5045,7 @@
         <v>32</v>
       </c>
       <c r="C262" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D262" t="s">
         <v>22</v>
@@ -5107,13 +5107,13 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
-        <v>105704.07995229975</v>
+        <v>118139.85406433501</v>
       </c>
       <c r="B266" t="s">
         <v>32</v>
       </c>
       <c r="C266" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D266" t="s">
         <v>16</v>
@@ -5124,27 +5124,27 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
-        <v>109849.33798964485</v>
+        <v>127956.7289673512</v>
       </c>
       <c r="B267" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C267" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D267" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E267" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
-        <v>124357.74112035264</v>
+        <v>93875.101649290853</v>
       </c>
       <c r="B268" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C268" t="s">
         <v>6</v>
@@ -5158,30 +5158,30 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
-        <v>113994.59602698994</v>
+        <v>63978.364483675607</v>
       </c>
       <c r="B269" t="s">
         <v>32</v>
       </c>
       <c r="C269" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D269" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E269" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
-        <v>118139.85406433501</v>
+        <v>124357.74112035264</v>
       </c>
       <c r="B270" t="s">
         <v>32</v>
       </c>
       <c r="C270" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D270" t="s">
         <v>16</v>
@@ -5192,30 +5192,30 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
-        <v>124357.74112035264</v>
+        <v>191935.0934510268</v>
       </c>
       <c r="B271" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C271" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D271" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E271" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
-        <v>130575.62817637029</v>
+        <v>98904.124951931444</v>
       </c>
       <c r="B272" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C272" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D272" t="s">
         <v>16</v>
@@ -5226,19 +5226,19 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
-        <v>122285.1121016801</v>
+        <v>63978.364483675607</v>
       </c>
       <c r="B273" t="s">
         <v>32</v>
       </c>
       <c r="C273" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D273" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E273" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
